--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0059.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0059.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Mutant Organism: Geohide Saurian Small</t>
+          <t>Sinh vật thể đột biến: Geohide Saurian Small</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Người Phụ Nữ Kiêu Ngạo</t>
+          <t>Người phụ nữ kiêu căng</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cô Gái Ẩn Mình</t>
+          <t>Cô Gái Bí Ẩn</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Snowfluff Seal</t>
+          <t>Ấn Chương Bông Tuyết</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Cluster Prism: Havoc</t>
+          <t>Lăng Kính Cụm: Havoc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>: Plenilune Sacrifice</t>
+          <t>: Hy Sinh Trăng Tròn</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hongjing</t>
+          <t>Hồng Kính</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>KU-Cannon</t>
+          <t>KU-Pháo</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Shadow of the Past</t>
+          <t>Bóng Tối Quá Khứ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ tiên quyết để tham gia</t>
+          <t>Hoàn thành nhiệm vụ tiền đề để tham gia</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>A Brief Log</t>
+          <t>Bản Ghi Ngắn</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Audio Log 1</t>
+          <t>Bản ghi âm số 1</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Waterlamp</t>
+          <t>Đèn Hoa Nước</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Flare Stone - Taunt Puzzle</t>
+          <t>Đá Lửa - Câu Đố Khiêu Khích</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Nightmare: Crownless</t>
+          <t>Ác Mộng: Crownless</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu lo lắng</t>
+          <t>Nhà Nghiên Cứu Lo Lắng</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Kẻ bị ruồng bỏ nơi vực sâu</t>
+          <t>: Kẻ Lưu Đày Vực Sâu</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Gondolier</t>
+          <t>Người Chèo Gondola</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Parody</t>
+          <t>Nhại lại</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Lingfeng</t>
+          <t>Lăng Phong</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Rock Mirror</t>
+          <t>Gương Đá</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Tianhu</t>
+          <t>Thiên Hổ</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Este</t>
+          <t>Thưa...</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Bird Egg</t>
+          <t>Trứng Chim</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Đặt lại và phát lại</t>
+          <t>Đặt lại và Phát lại</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Xinyang</t>
+          <t>Tân Dương</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Thông báo tìm thẻ sinh viên bị mất</t>
+          <t>Thông Báo về Mất Thẻ Học Sinh</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Tương Tác</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Fixed Grapple</t>
+          <t>Móc cố định đã sửa</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Vào Sonoro Sphere</t>
+          <t>Bước vào Sonoro Sphere</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Nhận lấy</t>
+          <t>Lấy đi</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Threnodian Contaminated Plant</t>
+          <t>Thực Vật Nhiễm Độc Threnodian</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Ordinary Wine List</t>
+          <t>Danh Sách Rượu Bình Thường</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Brant Cube</t>
+          <t>Khối Brant</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Nightmare: Thundering Mephis - Talons of Delirium</t>
+          <t>Ác Mộng: Thundering Mephis - Talons of Delirium</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Dungeon_Air Wall Manager_Combination</t>
+          <t>Quản lý Rào Cản Không Gian_Kết Hợp</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Battered Gladiator</t>
+          <t>Đấu Sĩ Tơi Bời</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Qinggong</t>
+          <t>Thanh Công</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Nói chuyện với nhân viên pha chế</t>
+          <t>Nói chuyện với người pha chế</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Jian</t>
+          <t>Kiên</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>The False Sovereign</t>
+          <t>Kẻ Quân Vương Giả Mạo</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Reactor Husk</t>
+          <t>Vỏ Lò Phản Ứng</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Ivory Gatekeeper</t>
+          <t>Lính Canh Cổng Ngà</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>"Alter Ego"</t>
+          <t>"Bản Ngã Khác"</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Concierge</t>
+          <t>Lễ Tân</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Purify</t>
+          <t>Tinh Luyện</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Aetherfin Sliding</t>
+          <t>Trượt Aetherfin</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>"Red Eagle"</t>
+          <t>"Đại Bàng Đỏ"</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Lan</t>
+          <t>Lan.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu tiên phong</t>
+          <t>Nhà Nghiên Cứu Tiên Phong</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Yongli</t>
+          <t>Dũng Lực</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Dragon of the Forlorn</t>
+          <t>Rồng của Nỗi Sầu</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Crafting</t>
+          <t>Đang chế tác</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Tick Tack Boy</t>
+          <t>Cậu Bé Tíc Tắc</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Đặt "viên ngọc" của Carlotta</t>
+          <t>Đặt "ngọc" của Carlotta</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Instructor Dashan</t>
+          <t>Huấn luyện viên Dashan</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Embers of Glory</t>
+          <t>: Than Hồng Của Vinh Quang</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Savanna</t>
+          <t>Thảo Nguyên</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Eee</t>
+          <t>Ê ê</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>: Phantom - Simulated Replica</t>
+          <t>: Phantom - Bản Sao Mô Phỏng</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Đi qua</t>
+          <t>Đi qua đi</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Gợi ý một bộ phim kinh dị</t>
+          <t>Gợi ý một bộ phim kinh dị đi</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Wenji</t>
+          <t>Văn Kì</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>"Kẻ sát nhân trong giấc mơ"</t>
+          <t>"Sát Thủ Trong Giấc Mơ"</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Thư từ Cung điện Ephor</t>
+          <t>Lá Thư Từ Cung Điện Ephor</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Gemberry</t>
+          <t>Quả Gemberry</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Ngồi vào ghế gần đuôi thuyền</t>
+          <t>Ngồi ghế gần đuôi tàu đi</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Voidspawn: Windlash Coleoid</t>
+          <t>Tacet Discord: Xoáy Gió Coleoid</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Lắng nghe</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Meticulous Acolyte</t>
+          <t>Tín Đồ Tỉ Mỉ</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Lắng nghe tiếng vang của chuyến săn cá voi</t>
+          <t>Hãy lắng nghe những âm vang của chuyến săn cá voi</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Đến lúc tấn công</t>
+          <t>Đến lúc tích năng lượng thôi!</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Tiếp tục nhiệm vụ "Thợ săn kiếm: Vùng hoang dã" để mở khóa</t>
+          <t>Tiếp tục nhiệm vụ "Thợ Săn Kiếm: Vùng Hoang Dã" để mở khóa</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Frostwing</t>
+          <t>Đôi Cánh Băng Giá</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Người phụ nữ dày dạn</t>
+          <t>Phụ Nữ Từng Trải</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Honglang</t>
+          <t>Hồng Lãng</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Bossrush Ground</t>
+          <t>Đấu Trường BossRush</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tôi muốn giao nộp một số đồ cổ</t>
+          <t>Tớ muốn giao nộp vài món đồ cổ.</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Exile A</t>
+          <t>Kẻ Lưu Đày A</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Tôi muốn mua một số món quà</t>
+          <t>Tao muốn mua vài món quà</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Destructible Vehicle</t>
+          <t>Xe có thể phá hủy</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Ác mộng của kẻ ô uế</t>
+          <t>Ác Mộng Nhiễm Độc</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Exile Cube</t>
+          <t>Khối Lưu Đày</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu lo lắng</t>
+          <t>Nhà Nghiên Cứu Lo Lắng</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Sad Gladiator</t>
+          <t>Đấu Sĩ Đau Lòng</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Cậu bé bi quan</t>
+          <t>Chàng Trai Bi Quan</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Xiaojue</t>
+          <t>Tiểu Quyết</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>To Second Floor</t>
+          <t>Tới Tầng Hai</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Tiger's Maw Ore</t>
+          <t>Quặng Hàm Hổ</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Smell</t>
+          <t>Mùi</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Mingzi</t>
+          <t>Minh Tử</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Neon Tower: Mê cung vòng lặp (Tiếp tục)</t>
+          <t>Tháp Neon: Mê Cung Vòng Lặp (Tiếp tục)</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Water Beetle</t>
+          <t>Bọ Nước</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Teleport</t>
+          <t>Dịch chuyển tức thời</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>"The Returned"</t>
+          <t>"Những Kẻ Trở Về"</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Thuyền trưởng cá mập cuồng tín</t>
+          <t>Thuyền Trưởng Cá Mập Cuồng Tín</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>KU-Goodie</t>
+          <t>KU-Thiện Lành</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Cooking Stove</t>
+          <t>Bếp Nấu</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Bắt đầu thu thập Khát Khao</t>
+          <t>Bắt đầu thu thập Khát Vọng</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Kẻ Khoe Khoang</t>
+          <t>Gã Đắc Ý</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Vực Sâu Cõi Ảo Ảnh</t>
+          <t>Vực Sâu Cõi Ảo</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Ký Ức Của Tai Họa</t>
+          <t>Ký Ức Của Thảm Họa</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Tianyu</t>
+          <t>Thiên Vũ</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>: "Nameless Evermore"</t>
+          <t>: "Vô Danh Vĩnh Hằng"</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Feilian Beringal: Pillar</t>
+          <t>Feilian Beringal: Cột Trụ</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Heavyhands</t>
+          <t>Bàn Tay Nặng Trịch</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Install</t>
+          <t>Lắp đặt</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Người Lính Nghiêm Túc</t>
+          <t>Lính Tuần Nghiêm Túc</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Dâng Hoa</t>
+          <t>Đặt hoa</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Whining Aix's Mire - Mực Nước Chính Câu Chuyện Dâng Cao Và Hạ Thấp</t>
+          <t>Bãi Lầy Aix Rên Rỉ - Mực nước chính truyện lên xuống</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Pinrong</t>
+          <t>Pinrồng</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Wangxiu</t>
+          <t>Vọng Tú</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Light Builder</t>
+          <t>Thợ Xây Ánh Sáng</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Voidwing Moth - Mechanism Echo</t>
+          <t>Bướm Voidwing - Tiếng Vọng Cơ Chế</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Xiaobao</t>
+          <t>Tiểu Bảo</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Tôi Muốn Mua Một Vài Thứ</t>
+          <t>Tớ muốn mua gì đó.</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Quay Lại Đền Tetragon</t>
+          <t>Quay lại Đền Tetragon</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bố Trí Mảng Vũ Trụ</t>
+          <t>Bố Trí Ma Trận Vũ Trụ</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Green Rabbit</t>
+          <t>Thỏ Xanh</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Một Bia Mộ Có Luceanite</t>
+          <t>Ngôi mộ có viên Luceanite</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Commoner Client - Actor 2</t>
+          <t>Khách hàng thường dân - Diễn viên 2</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Gang Member's Notes</t>
+          <t>Ghi Chép Của Thành Viên Bang</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Nhận Phần Thưởng</t>
+          <t>Nhận thưởng</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Water Lily</t>
+          <t>Hoa Súng</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Hạn Chế Gondola Không Được Ủy Quyền Trong Thành Phố</t>
+          <t>Cấm Gondola không phận sự vào thành phố</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Dungeon 89</t>
+          <t>Hầm 89</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Cô Gái Nhút Nhát</t>
+          <t>Cô gái rụt rè</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Lingdi</t>
+          <t>Linh Đê</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Thành Viên Hội Overtonic</t>
+          <t>Thành viên Hội Overtonic</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Tacetite Fulminate Base</t>
+          <t>Nền Sấm Sét Tacetite</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Play Channel 2</t>
+          <t>Phát Kênh 2</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Mời Đấu Một Trận</t>
+          <t>Mời thách đấu</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Fitness Influencer</t>
+          <t>Người Ảnh Hưởng Thể Hình</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Mining Reindeer</t>
+          <t>Tuần Lộc Khai Thác</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Freshmen Instructor</t>
+          <t>Giảng viên Tân binh</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Chonglin</t>
+          <t>Sùng Lâm</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Ruin Gate</t>
+          <t>Cổng Tàn Tích</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Nói chuyện với Lifer</t>
+          <t>Nói chuyện với Người Tù</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Clemency</t>
+          <t>Khoan dung</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Nightmare: Dwarf Cassowary</t>
+          <t>Ác Mộng: Đà Điểu Lùn</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Một Tấm Thiệp Viết Tay Đẹp</t>
+          <t>Một bức thư tay xinh đẹp</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Novelli</t>
+          <t>Tiểu Thuyết Gia</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Onlooker</t>
+          <t>Người xem</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Jiaming</t>
+          <t>Gia Minh</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Bắt Đầu Máy Gacha</t>
+          <t>Bắt đầu Máy Gacha</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Fluffguin</t>
+          <t>Chim cánh cụt bông</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Basic Supply Chest</t>
+          <t>Rương Vật Tư Cơ Bản</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Thùng phá hủy được</t>
+          <t>Thùng phi có thể phá hủy</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Học sinh thất lạc</t>
+          <t>Học Sinh Mất Tích</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Mảnh kính màu</t>
+          <t>Mảnh Kính Màu</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nhân viên lễ tân</t>
+          <t>Nhân viên Tiếp Tân</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Thunder Ursa</t>
+          <t>Gấu Bắc Cực Sấm Sét</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Midnight Ranger</t>
+          <t>Kỵ Sĩ Bóng Đêm</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Sparkling Memories</t>
+          <t>Ký Ức Lấp Lánh</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Vào Đại sảnh Hội nghị</t>
+          <t>Bước vào Hội Trường</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Fluorite</t>
+          <t>Huỳnh Thạch</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Rover Cube</t>
+          <t>Khối Lập Phương của Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Wenting</t>
+          <t>Văn Đình</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Xinxin</t>
+          <t>Tân Tân</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Talk</t>
+          <t>Nói chuyện</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Summon Gondola</t>
+          <t>Triệu hồi Gondola</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Stellar Orbit Beats</t>
+          <t>Nhịp Quỹ Đạo Tinh Tú</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Bắt đầu vẽ tranh</t>
+          <t>Bắt đầu vẽ nào</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Empty Range Entity</t>
+          <t>Thực Thể Phạm Vi Trống</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Trở về Phía Bóng Tối</t>
+          <t>Trở lại Bóng Tối</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Rogue: Self-Destruct Monster</t>
+          <t>Kẻ Đi Lang Thang: Quái Vật Tự Hủy</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Chop Chop: Headless</t>
+          <t>Chop Chop: Không Đầu</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Researcher Garcia</t>
+          <t>Nhà nghiên cứu Garcia</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Qiangong</t>
+          <t>Cương Công</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Lingfeng</t>
+          <t>Lăng Phong</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>The Refiner</t>
+          <t>Người Tinh Chế</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Quý bà tinh tế</t>
+          <t>Quý Cô Tinh Tế</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Zhuming</t>
+          <t>Chủ Minh</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Miks</t>
+          <t>Các Miko</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Sound Emulator</t>
+          <t>Bộ Mô Phỏng Âm Thanh</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu cảnh giác</t>
+          <t>Nhà nghiên cứu báo động!</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Re</t>
+          <t>Tái</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Bajorn Sheep</t>
+          <t>Cừu Bajorn</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Yanning</t>
+          <t>Yến Ninh</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>A Message</t>
+          <t>Một Tin Nhắn</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Sự kiện Tactical Simulacra đã kết thúc</t>
+          <t>Sự kiện Tạc Ảnh Chiến Thuật đã kết thúc</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Glowing Mourning Aix</t>
+          <t>Aix Tang Lễ Phát Quang</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Flora Drone</t>
+          <t>Drone Flora</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Thợ săn</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nâng Cấp Quyền Truy Cập</t>
+          <t>Nâng cấp Xóa Sổ</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Ragunna Gondolier</t>
+          <t>Người Chèo Gondola Ragunna</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Phantom: Chop Chop</t>
+          <t>Bóng Ma: Chặt Chém</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Điều tra ô nhiễm Voidmatter</t>
+          <t>Điều tra sự ô nhiễm Voidmatter</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Dark Mage</t>
+          <t>Pháp Sư Hắc Ám</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Coordinates Designation</t>
+          <t>Chỉ định tọa độ</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Spacetrek Convoy Vật tư</t>
+          <t>Vật tư Đoàn vận tải Spacetrek</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Border Patrol</t>
+          <t>Tuần Tra Biên Giới</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Ký ức của Người Vô Danh</t>
+          <t>Ký Ức Vô Danh</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>(Contaminated)</t>
+          <t>(Đã nhiễm độc...)</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Enter Mianloong Chamber</t>
+          <t>Vào Phòng Mianloong</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Elevator Console</t>
+          <t>Bảng Điều Khiển Thang Máy</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Drift</t>
+          <t>Trôi dạt</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Đắm chìm vào giấc mơ</t>
+          <t>Đắm Chìm Vào Giấc Mơ</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Jiuli</t>
+          <t>Cửu Ly</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Cậu bé lạc</t>
+          <t>Cậu Bé Lạc Loài</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>The Unknown Wine List</t>
+          <t>Danh Sách Rượu Bí Ẩn</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Đến tầng trên</t>
+          <t>Lên tầng trên</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Tham gia "Thử thách Giả mạo"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27314,7 +27314,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Mad Knight</t>
+          <t>Hiệp Sĩ Điên</t>
         </is>
       </c>
       <c r="N384" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Meteoric Iron</t>
+          <t>Thiết Thiên Thạch</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Shadow Stepper</t>
+          <t>Bước Bóng</t>
         </is>
       </c>
       <c r="N391" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Angry Instructor</t>
+          <t>Huấn Luyện Viên Giận Dữ</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Thành viên Black Shores</t>
+          <t>Thành Viên Bờ Đen</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Timid Acolyte</t>
+          <t>Tín Đồ Nhút Nhát</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Middle-aged Listener</t>
+          <t>Người Lắng Nghe Trung Niên</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Xem đi</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Shuoxing</t>
+          <t>Sao Tinh</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Academic Committee Supervisor</t>
+          <t>Giám Sát Ủy Ban Học Thuật</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Yingzhu</t>
+          <t>Doanh Chúc</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chop Chop: Rightless</t>
+          <t>Chop Chop: Không Tay Phải</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>"Obsession"</t>
+          <t>"Nỗi Ám Ảnh"</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Ebony Gatekeeper</t>
+          <t>Người Gác Cổng Hắc Ám</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Bloodtear Warrior</t>
+          <t>Chiến Binh Máu Lệ</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Hurriclaw Alpha</t>
+          <t>Bão Vuốt Alpha</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Drunk Gladiator</t>
+          <t>Đấu Sĩ Say Rượu</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đạt Cấp 5 Reach Data Hub để mở khóa</t>
+          <t>Mở khóa khi đạt Cấp Trung Tâm Dữ Liệu 5</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Mở đường đến khán đài</t>
+          <t>Mở lối vào khu vực khán giả</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Ziheng</t>
+          <t>Tử Hành</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Insert</t>
+          <t>Chèn</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Mời bạn đồng hành xem phim</t>
+          <t>Mời bạn bè cùng xem phim</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Vận hành</t>
+          <t>Thao Tác</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Snow Owl</t>
+          <t>Cú Tuyết</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Absorb</t>
+          <t>Hấp Thu</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Dư</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Supply Chests</t>
+          <t>Các Rương Vật Tư</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Jingyu</t>
+          <t>Tinh Vũ</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Professor Edgar</t>
+          <t>Giáo sư Edgar</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Range Designation</t>
+          <t>Phạm Vi Chỉ Định</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Xem ghi chú do Ahab để lại</t>
+          <t>Xem lời nhắn Ahab để lại.</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Cô Bé Tò Mò</t>
+          <t>Cô bé tò mò</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Cunning Outcast</t>
+          <t>Kẻ Bị Ruồng Bỏ Xảo Quyệt</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Leave Averardo Vault</t>
+          <t>Rời khỏi Kho Báu Averardo</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nhật Ký từ Đại Tư Lệnh</t>
+          <t>Nhật Ký của Đại Chỉ Huy</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Excited Adventurer</t>
+          <t>Nhà Thám Hiểm Hào Hứng</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Thử Thách: Thăng Hoa Pha: III</t>
+          <t>Thử Thách: Thăng Hoa Giai Đoạn III</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Lament Recon: Chiến Binh Solaris</t>
+          <t>Thám Sát Âm Than: Lính Solaris</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Chờ các thành viên băng nhóm xuất hiện</t>
+          <t>Chờ bọn xã hội đen xuất hiện</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Hualin</t>
+          <t>Hoa Lâm</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Jingzhi</t>
+          <t>Tinh Chi</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Một cánh cửa đã được mở khóa ở đâu đó</t>
+          <t>Một cánh cửa vừa được mở khóa ở đâu đó.</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Vào Mind Dive Arcade</t>
+          <t>Bước vào Khu Vực Tâm Trí Ảo</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Wooly White</t>
+          <t>Cừu Trắng Lông Xù</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Hug</t>
+          <t>Ôm</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Đến Nightmare Nest</t>
+          <t>Đến Tổ Ác Mộng</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Ferocious Dog</t>
+          <t>Chó Dữ</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Siran</t>
+          <t>Siran...</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Phantom: Capitaneus</t>
+          <t>Bóng Ma: Capitaneus</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Điều tra chiếc hộp gỗ</t>
+          <t>Kiểm tra chiếc hộp gỗ</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Central Hub</t>
+          <t>Trung Tâm Điều Hành</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Xem trang nhật ký bí ẩn</t>
+          <t>Xem trang nhật ký bí ẩn.</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Curious Spectator</t>
+          <t>Người Tò Mò</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Chuyển sang không gian Starwhale</t>
+          <t>Chuyển sang không gian nền Cá Voi Ngôi Sao</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Chơi "Vernal Days Dreamed by the Star"</t>
+          <t>Phát "Giấc Mơ Ngày Xuân Dưới Ngôi Sao"</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Liondance Troupe Leader Huaze</t>
+          <t>Trưởng Đoàn Múa Lân - Huaze</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Khởi động Capsule Machine</t>
+          <t>Bắt đầu Máy Capsule</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Box</t>
+          <t>Thùng</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Đứa Trẻ Đóng Vai Hiệp Sĩ</t>
+          <t>Đứa trẻ đóng vai hiệp sĩ</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Mysterious Access Door</t>
+          <t>Cánh Cửa Truy Cập Bí Ẩn</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Laurus Gazelle</t>
+          <t>Linh Dương Laurus</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Firefly Swarm</t>
+          <t>Bầy Đom Đóm Lửa</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Xem ghi chú do Ahab để lại</t>
+          <t>Xem lời nhắn Ahab để lại.</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Presenter</t>
+          <t>Người dâng lễ</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>the Fifth</t>
+          <t>: Đệ Ngũ</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Kiểm tra dấu vết</t>
+          <t>Xem xét những dấu vết</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Bàn Thờ Hòa Âm</t>
+          <t>Bệ Phối Khí</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Commoner Client - Actor 3</t>
+          <t>Khách hàng thường dân - Diễn viên 3</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
